--- a/sim_proj_updated/trend_data.xlsx
+++ b/sim_proj_updated/trend_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="132" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="176" uniqueCount="33">
   <si>
     <t>Parameter</t>
   </si>
@@ -97,6 +97,21 @@
   </si>
   <si>
     <t>Slope</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Coliform</t>
+  </si>
+  <si>
+    <t>E. coli</t>
   </si>
 </sst>
 </file>
@@ -150,7 +165,7 @@
     <col min="3" max="3" width="13.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="10.7109375" customWidth="true"/>
-    <col min="6" max="6" width="6.140625" customWidth="true"/>
+    <col min="6" max="6" width="16.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,7 +190,7 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" s="0">
         <v>-76</v>
@@ -190,7 +205,7 @@
         <v>24</v>
       </c>
       <c r="F2" s="0">
-        <v>0</v>
+        <v>-0.085714285714285784</v>
       </c>
     </row>
     <row r="3">
@@ -210,7 +225,7 @@
         <v>25</v>
       </c>
       <c r="F3" s="0">
-        <v>0</v>
+        <v>0.086363636363636295</v>
       </c>
     </row>
     <row r="4">
@@ -230,7 +245,7 @@
         <v>25</v>
       </c>
       <c r="F4" s="0">
-        <v>0</v>
+        <v>-0.00041666666666658375</v>
       </c>
     </row>
     <row r="5">
@@ -250,7 +265,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="0">
-        <v>0</v>
+        <v>-0.0020833333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -270,7 +285,7 @@
         <v>26</v>
       </c>
       <c r="F6" s="0">
-        <v>0</v>
+        <v>0.034615384615384631</v>
       </c>
     </row>
     <row r="7">
@@ -290,7 +305,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="0">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8">
@@ -310,7 +325,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="0">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="9">
@@ -330,7 +345,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="0">
-        <v>0</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="10">
@@ -350,7 +365,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="0">
-        <v>0</v>
+        <v>-0.21428571428571427</v>
       </c>
     </row>
     <row r="11">
@@ -370,7 +385,7 @@
         <v>24</v>
       </c>
       <c r="F11" s="0">
-        <v>0</v>
+        <v>-20.399999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -390,12 +405,12 @@
         <v>25</v>
       </c>
       <c r="F12" s="0">
-        <v>0</v>
+        <v>-10.428571428571429</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B13" s="0">
         <v>-46</v>
@@ -410,7 +425,7 @@
         <v>25</v>
       </c>
       <c r="F13" s="0">
-        <v>0</v>
+        <v>-13.076923076923077</v>
       </c>
     </row>
     <row r="14">
@@ -430,12 +445,12 @@
         <v>25</v>
       </c>
       <c r="F14" s="0">
-        <v>0</v>
+        <v>-47.291666666666664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B15" s="0">
         <v>-47</v>
@@ -450,7 +465,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="0">
-        <v>0</v>
+        <v>-102.5</v>
       </c>
     </row>
     <row r="16">
@@ -510,12 +525,12 @@
         <v>24</v>
       </c>
       <c r="F18" s="0">
-        <v>0</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B19" s="0">
         <v>27</v>
@@ -535,7 +550,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B20" s="0">
         <v>27</v>
